--- a/Primo_dataLayer_テスト仕様書.xlsx
+++ b/Primo_dataLayer_テスト仕様書.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,13 +56,8 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -72,11 +67,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A3A5C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E86AB"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,7 +104,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -123,9 +112,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -493,18 +479,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,35 +508,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>対象イベント/機能</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -567,23 +565,39 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>GTMスニペット（head）の設置</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>GTM head</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>20260717</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,23 +612,39 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>GTMスニペット（body noscript）の設置</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>GTM body</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>20260717</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -629,23 +659,39 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>User-ID初期化がGTMスニペットより前に実行される</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>実装順序</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>20260717</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -660,59 +706,81 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>dataLayer初期化処理</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>dataLayer init</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>20260717</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-010</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>共通ページ計測</t>
+          <t>GTM基本設定</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ログイン時：user_id/area_id/staff_id/member_r送信</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>共通push</t>
+          <t>GTMスニペットが1回のみ設置されている</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>GTM head</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-011</t>
+          <t>TC-010</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -722,28 +790,44 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>未ログイン時：user_idキーを出力しない</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>ログイン時：user_id/area_id/staff_id/member_r送信</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>共通push</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>20260718</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-012</t>
+          <t>TC-011</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -753,28 +837,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>member_rの数値マッピング（0〜3）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>member_r</t>
+          <t>未ログイン時：user_idキーを出力しない</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
+          <t>共通push</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>20260718</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-013</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -784,90 +884,128 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ページリロード時のdataLayer再出力</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>共通push</t>
+          <t>member_rの数値マッピング（0〜3）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>member_r</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>20260718</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-020</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>認証</t>
+          <t>共通ページ計測</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ログイン成功時にloginイベント送信</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>ページリロード時のdataLayer再出力</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+          <t>共通push</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>20260718</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>小園</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-021</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>認証</t>
+          <t>共通ページ計測</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ログイン失敗時はloginイベントを送信しない</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>通常ページ表示時にloginイベントを送信しない</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>login</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-022</t>
+          <t>TC-020</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -877,1048 +1015,1794 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>会員登録成功時にsign_upイベント送信</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>sign_up</t>
+          <t>ログイン成功時にloginイベント送信</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-030</t>
+          <t>TC-021</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>リード</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>見積書DL時にquote_downloadイベント送信</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>quote_download</t>
+          <t>ログイン失敗時はloginイベントを送信しない</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-031</t>
+          <t>TC-022</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>リード</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>見積依頼成功時：generate_lead（lead_source=quote）+items</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>generate_lead</t>
+          <t>会員登録成功時にsign_upイベント送信</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>sign_up</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-032</t>
+          <t>TC-023</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>リード</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>問い合わせ成功時：generate_lead（lead_source=inquiry）</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>generate_lead</t>
+          <t>会員登録失敗時はsign_upイベントを送信しない</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>sign_up</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-033</t>
+          <t>TC-024</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>リード</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>再見積（re_quote）時はgenerate_leadを送信しない</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>generate_lead</t>
+          <t>会員登録成功時：mailmagazine_signup（subscription_status=all）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>mailmagazine_signup</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-040</t>
+          <t>TC-025</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>商品詳細表示時：view_item + stock</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>view_item</t>
+          <t>会員登録成功時：mailmagazine_signup（subscription_status=text_only）</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
+          <t>mailmagazine_signup</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-041</t>
+          <t>TC-026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>カート追加成功時：add_to_cart（add_method=normal）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>add_to_cart</t>
+          <t>会員登録成功時：mailmagazine_signup（subscription_status=none）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
+          <t>mailmagazine_signup</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-042</t>
+          <t>TC-027</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>認証</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>add_to_cart：add_method=quick_order</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>add_to_cart</t>
+          <t>会員登録失敗時はmailmagazine_signupを送信しない</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
+          <t>mailmagazine_signup</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-043</t>
+          <t>TC-030</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>リード</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>add_to_cart：add_method=order_history</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>add_to_cart</t>
+          <t>見積書DL時にquote_downloadイベント送信</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+          <t>quote_download</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-044</t>
+          <t>TC-031</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>リード</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>add_to_cart：add_method=quote_history</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>add_to_cart</t>
+          <t>見積依頼成功時：generate_lead（lead_source=quote）+items</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+          <t>generate_lead</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-045</t>
+          <t>TC-032</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>リード</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>カート削除時：remove_from_cart</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>remove_from_cart</t>
+          <t>問い合わせ成功時：generate_lead（lead_source=inquiry）</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>generate_lead</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-046</t>
+          <t>TC-033</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>リード</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>お気に入り追加時：add_to_wishlist</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>add_to_wishlist</t>
+          <t>再見積（re_quote）時はgenerate_leadを送信しない</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>generate_lead</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-047</t>
+          <t>TC-034</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>商品・カート</t>
+          <t>リード</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ecommerceイベント前にecommerce:nullをpush</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ecommerce clear</t>
+          <t>見積依頼バリデーションエラー時はgenerate_leadを送信しない</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>generate_lead</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-050</t>
+          <t>TC-035</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>購入フロー</t>
+          <t>リード</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>注文プロセス開始：begin_checkout（cart_type=normal）</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>begin_checkout</t>
+          <t>問い合わせ送信失敗時はgenerate_leadを送信しない</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>generate_lead</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-051</t>
+          <t>TC-040</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>購入フロー</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>begin_checkout（cart_type=quote）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>begin_checkout</t>
+          <t>商品詳細表示時：view_item + stock</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>view_item</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-052</t>
+          <t>TC-041</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>購入フロー</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>request_item_countの値（あり/なし=0）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>begin_checkout</t>
+          <t>カート追加成功時：add_to_cart（add_method=normal）</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
+          <t>add_to_cart</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-060</t>
+          <t>TC-042</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>購入フロー</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>add_shipping_infoとadd_payment_infoの同時送信</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>add_shipping_info/add_payment_info</t>
+          <t>add_to_cart：add_method=quick_order</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
+          <t>add_to_cart</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-061</t>
+          <t>TC-043</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>購入フロー</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>payment_typeの値（4種）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>add_payment_info</t>
+          <t>add_to_cart：add_method=order_history</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>add_to_cart</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-062</t>
+          <t>TC-044</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>購入フロー</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>クーポンコード（ecommerce.coupon）の送信</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>add_shipping_info/add_payment_info</t>
+          <t>add_to_cart：add_method=quote_history</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>add_to_cart</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-070</t>
+          <t>TC-045</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>注文確定</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>承認申請時：approval_request（order_id）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>approval_request</t>
+          <t>カート削除時：remove_from_cart</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>remove_from_cart</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-071</t>
+          <t>TC-046</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>注文確定</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>注文確定時：purchase（承認なし）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>purchase</t>
+          <t>お気に入り追加時：add_to_wishlist</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>add_to_wishlist</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TC-072</t>
+          <t>TC-047</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>注文確定</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>承認あり：承認完了時にpurchase送信</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>purchase</t>
+          <t>ecommerceイベント前にecommerce:nullをpush</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>ecommerce clear</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-073</t>
+          <t>TC-048</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>注文確定</t>
+          <t>商品・カート</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>決済エラー時はpurchaseを送信しない</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>purchase</t>
+          <t>カート追加失敗時はadd_to_cartを送信しない</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>add_to_cart</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TC-074</t>
+          <t>TC-050</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>注文確定</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>customer_type（new/returning/guest）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>purchase</t>
+          <t>注文プロセス開始：begin_checkout（cart_type=normal）</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>begin_checkout</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-075</t>
+          <t>TC-051</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>注文確定</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>order_id = transaction_id = approval_request.order_id</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>purchase/approval_request</t>
+          <t>begin_checkout（cart_type=quote）</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>begin_checkout</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TC-080</t>
+          <t>TC-052</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>mailmagazine_signup（all/text_only/none）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>mailmagazine_signup</t>
+          <t>request_item_countの値（あり/なし=0）</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>begin_checkout</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-081</t>
+          <t>TC-060</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>一括注文フォーマットDL：bulk_order_download</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>bulk_order_download</t>
+          <t>add_shipping_infoとadd_payment_infoの同時送信</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>add_shipping_info/add_payment_info</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TC-082</t>
+          <t>TC-061</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>一括注文アップロード成功：bulk_order_upload + add_to_cart複数</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>bulk_order_upload</t>
+          <t>payment_typeの値（4種）</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
+          <t>add_payment_info</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-083</t>
+          <t>TC-062</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>一括注文アップロード失敗：bulk_order_uploadのみ（add_to_cartなし）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>bulk_order_upload</t>
+          <t>クーポン適用時：ecommerce.couponの送信</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
+          <t>add_shipping_info/add_payment_info</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TC-084</t>
+          <t>TC-063</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>error_typeの複数値（カンマ区切り）</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>bulk_order_upload</t>
+          <t>クーポン未適用時：couponキーを出力しない</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>add_shipping_info/add_payment_info</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-090</t>
+          <t>TC-064</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>items配列</t>
+          <t>購入フロー</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>items共通フィールドの存在・型</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>配送・決済情報のサーバー受理失敗時はadd_shipping_info/add_payment_infoを送信しない</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>add_shipping_info/add_payment_info</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TC-091</t>
+          <t>TC-070</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>items配列</t>
+          <t>注文確定</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>item_variantなし時はキーごと省略</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>承認申請時：approval_request（order_id）</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
+          <t>approval_request</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>注文確定</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>注文確定時：purchase（承認なし）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>注文確定</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>承認あり：承認完了時にpurchase送信</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>注文確定</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>決済エラー時はpurchaseを送信しない</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>注文確定</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>customer_type（new/returning/guest）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>注文確定</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>order_id = transaction_id = approval_request.order_id</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>purchase/approval_request</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>注文確定</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>承認不要の注文でapproval_requestを送信しない</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>approval_request</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>注文確定</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>承認申請のみではpurchaseを送信しない</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TC-080</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>マイページ：mailmagazine_signup（all/text_only/none）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>mailmagazine_signup</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TC-081</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>一括注文フォーマットDL：bulk_order_download</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>bulk_order_download</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>一括注文アップロード成功：bulk_order_upload + add_to_cart複数</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>bulk_order_upload</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>一括注文アップロード失敗：bulk_order_uploadのみ（add_to_cartなし）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>bulk_order_upload</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TC-084</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>error_typeの複数値（カンマ区切り）</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>bulk_order_upload</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>マイページ：メルマガ設定保存失敗時はmailmagazine_signupを送信しない</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>mailmagazine_signup</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>TC-090</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>items配列</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>items共通フィールドの存在・型</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TC-091</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>items配列</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>item_variantなし時はキーごと省略</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>TC-092</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>items配列</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>サプライヤー異なる商品は別要素として配列に含む</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>items</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>【凡例】</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>種別: 正常=成功時に送信 / 異常=失敗時・非該当時に送信しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>エビデンス: Consoleスクショ・GTMプレビュー・ページソースのファイル名を記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>実施結果: OK / NG / 未実施 / 保留</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>対象サイト: primo-demo2-front.ec-rider2-demo.net</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>GTMコンテナID: GTM-TGF9D8WX</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>テスト環境: 手動テスト（ブラウザDevTools Console）</t>
         </is>
       </c>
     </row>
@@ -1933,17 +2817,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1954,41 +2841,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-080</t>
@@ -1996,34 +2898,41 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【中】mailmagazine_signup（all/text_only/none）</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>メルマガ設定変更可能（会員登録時 or マイページ）</t>
+          <t>【中】マイページ：mailmagazine_signup（all/text_only/none）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ログイン済み。マイページでメルマガ設定変更可能</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. 受信設定を「全て受け取る」「テキストのみ」「受け取らない」にそれぞれ変更
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'mailmagazine_signup').map(d =&gt; d.subscription_status)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>['all'] / ['text_only'] / ['none'] がそれぞれ対応する</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-081</t>
@@ -2031,34 +2940,41 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】一括注文フォーマットDL：bulk_order_download</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>一括注文画面にアクセス可能</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. 一括注文フォーマット（CSV）をDL
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'bulk_order_download')</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>例: [{event:'bulk_order_download'}]</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-082</t>
@@ -2066,35 +2982,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【高】一括注文アップロード成功：bulk_order_upload + add_to_cart複数</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>正しいCSVファイルを用意</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>正しいCSVファイル</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. 一括注文CSVをアップロードして成功
 2. カート画面遷移後、Consoleで確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>({ upload: dataLayer.filter(d =&gt; d.event === 'bulk_order_upload'), carts: dataLayer.filter(d =&gt; d.event === 'add_to_cart' &amp;&amp; d.add_method === 'bulk_order') })</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>upload: [{event:'bulk_order_upload', upload_status:'success'}]
 carts: アップロードした全商品分のadd_to_cartが存在し、add_method='bulk_order'</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-083</t>
@@ -2102,35 +3025,42 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>【高】一括注文アップロード失敗：bulk_order_uploadのみ（add_to_cartなし）</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>エラーになるCSVファイルを用意（在庫不足等）</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>エラーになるCSV</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. 不正/エラーCSVをアップロード
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>({ upload: dataLayer.filter(d =&gt; d.event === 'bulk_order_upload'), carts: dataLayer.filter(d =&gt; d.event === 'add_to_cart') })</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>upload: [{event:'bulk_order_upload', upload_status:'error', error_type:'...'}]
 carts: add_to_cartは追加されない</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="120" customHeight="1">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-084</t>
@@ -2138,32 +3068,82 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>【中】error_typeの複数値（カンマ区切り）</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>複数エラーが同時に発生するCSV</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. 数量公倍数エラー+在庫不足等の複合エラーCSVをアップロード
 2. error_typeを確認</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'bulk_order_upload').pop().error_type</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>カンマ区切りで複数エラー（例: 'quantity_invalid_multiple,insufficient_stock'）</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>【中】マイページ：メルマガ設定保存失敗時はmailmagazine_signupを送信しない</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>マイページでメルマガ設定変更可能</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1. 操作前の件数を記録
+2. 保存失敗（バリデーションエラー等）を発生
+3. 件数を比較</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'mailmagazine_signup').length</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>失敗操作後も件数が増えない。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2176,17 +3156,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2197,41 +3180,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-090</t>
@@ -2239,35 +3237,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】items共通フィールドの存在・型</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>ecommerce.itemsを含む任意イベント発火済み</t>
-        </is>
-      </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce.items を含むイベント発火済み</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. view_itemまたはadd_to_cartを発火
 2. items[0]のフィールドを確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Object.keys(dataLayer.find(d =&gt; d.ecommerce?.items).ecommerce.items[0])</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>['item_id','item_name','item_brand','item_category1','item_category2','item_category3','item_category4','item_category5','price','quantity'] が含まれる。
 price/quantityは数値型。</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-091</t>
@@ -2275,34 +3280,41 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【中】item_variantなし時はキーごと省略</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>バリエーション（サイズ・色）がない商品</t>
-        </is>
-      </c>
       <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>バリエーションなし商品</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. バリエーションなし商品の詳細を表示
 2. itemsを確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>'item_variant' in dataLayer.find(d =&gt; d.event === 'view_item').ecommerce.items[0]</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>false（item_variantキー自体が存在しない）。</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-092</t>
@@ -2310,32 +3322,39 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【中】サプライヤー異なる商品は別要素として配列に含む</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>異なるサプライヤーの商品を同時にカート追加可能</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. サプライヤーAとBの商品をカートに追加
 2. items配列を確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_to_cart').pop().ecommerce.items.map(i =&gt; i.item_brand)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>配列に異なるサプライヤー名が別要素として含まれる（例: ['エビス倉庫', '別サプライヤー']）</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2348,7 +3367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2357,289 +3376,229 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Primo dataLayer 手動テスト実施手順</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
+      <c r="A2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>■ 事前準備</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>1. Chrome（推奨）で対象サイトにアクセス</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2. F12 → Consoleタブを開く</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>3. ページ遷移でdataLayerがリセットされるため、操作前にConsoleを開いた状態で実施</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>3. 異常系テストは操作前後でイベント件数を比較する</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4. Networkタブで「gtm」「collect」等のリクエストも併せて確認するとより確実</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>4. 未ログイン確認はシークレットウィンドウまたは Ctrl+Shift+R を使用</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
+      <c r="A8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>■ 基本確認コマンド</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>コマンド</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>期待される出力例</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>dataLayer</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>dataLayer全体を表示</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>配列 [{...}, {...}, ...]</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'イベント名')</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>特定イベントを抽出</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>該当イベントの配列</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>JSON.stringify(dataLayer, null, 2)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>整形して全体表示</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>読みやすいJSON形式</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'イベント名').length</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>件数比較（異常系）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>操作前後で増えないこと</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>dataLayer.filter(d =&gt; d.event === 'イベント名')</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>特定イベントを抽出</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>該当イベントの配列</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>dataLayer.find(d =&gt; d.user_id)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>user_id付きpush</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>{user_id, area_id, staff_id, member_r}</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>dataLayer.filter(d =&gt; d.event === 'イベント名').pop()</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>直近の該当イベント</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>最新1件のオブジェクト</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; 'user_id' in d)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>未ログイン確認</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>dataLayer.find(d =&gt; d.user_id)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>user_id付きpushを取得</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>{user_id:'...', area_id:'...', ...}</t>
-        </is>
-      </c>
+      <c r="A15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>dataLayer.filter(d =&gt; 'user_id' in d)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>user_idキーの有無確認</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>未ログイン時は []</t>
+          <t>■ 注意事項</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>(() =&gt; { const i = dataLayer.findIndex(d =&gt; d.event === 'EVENT'); return i&gt;=1 ? dataLayer[i-1] : null; })()</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>ecommerce:null確認</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>{ecommerce: null}</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>・gtm.uniqueEventId は GTM が自動付与。実装の余計なキーとはみなさない</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>・noscript（TC-002）はページソース（Ctrl+U）で確認。querySelector は使わない</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>■ GTM設置確認コマンド</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>・TC-003 はページソースの記述順序 + dataLayer 順序で確認</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>document.querySelector('script[src*="googletagmanager.com/gtm.js"]')</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>head内GTMスニペット</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>HTMLScriptElement（nullでない）</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>・Turbo遷移直後は旧 dataLayer が残ることがある。フルリロードで判定</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>document.querySelector('noscript iframe[src*="googletagmanager.com/ns.html"]')</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>body内noscript</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>iframe要素（nullでない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>・異常系は『イベントが送信されない』ことを確認する</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>■ 判定基準</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>■ エビデンス取得手順</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>・event名が指示書と完全一致（大文字小文字区別）</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>1. Console確認: コマンド実行結果が見えるようスクショを取得</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>・数値項目（price, quantity, stock, member_r等）は文字列ではなく数値型</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2. ページソース確認: Ctrl+U の該当箇所をスクショ、またはファイル名を記載</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>・未ログイン時はuser_idキー自体を出力しない（推奨仕様①）</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>3. GTMプレビュー: イベント発火画面をスクショ</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>・値が存在しない任意項目はキーごと省略（nullではなくキー非出力）</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>4. ファイル名例: TC-020_login_console.png / TC-002_noscript_source.png</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>・ecommerce系イベントの直前に {ecommerce: null} がpushされている</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>・JSONの最後の要素に余分なカンマがない（構文エラーなし）</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>5. 詳細シートの「実際の出力結果」にConsole出力をコピペしても可</t>
         </is>
       </c>
     </row>
@@ -2657,17 +3616,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2678,41 +3640,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-001</t>
@@ -2720,35 +3697,46 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】GTMスニペット（head）の設置</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>対象サイト（primo-demo2-front.ec-rider2-demo.net）の任意ページにアクセスできること</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. ブラウザで任意ページを開く
 2. ページソースまたはDevTools Elementsで&lt;head&gt;内を確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>document.querySelector('script[src*="googletagmanager.com/gtm.js"]')</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>null以外の要素が返る。src属性に「GTM-TGF9D8WX」が含まれる。
 例: HTMLScriptElement { src: "https://www.googletagmanager.com/gtm.js?id=GTM-TGF9D8WX" }</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-002</t>
@@ -2756,33 +3744,46 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】GTMスニペット（body noscript）の設置</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. ページソースまたはElementsで&lt;body&gt;直後を確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>document.querySelector('noscript iframe[src*="googletagmanager.com/ns.html"]')</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>null以外のiframe要素が返る。srcに「GTM-TGF9D8WX」が含まれる。</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+          <t>（コマンド不要）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>&lt;body&gt; 直後に以下が存在すること：
+&lt;!-- Google Tag Manager (noscript) --&gt;
+&lt;noscript&gt;&lt;iframe src="https://www.googletagmanager.com/ns.html?id=GTM-TGF9D8WX" ...&gt;&lt;/iframe&gt;&lt;/noscript&gt;</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-003</t>
@@ -2790,35 +3791,45 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【高】User-ID初期化がGTMスニペットより前に実行される</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ログイン済み状態</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. ページソースの&lt;head&gt;内でスクリプトの記述順序を確認
 2. user_id初期化のdataLayer.pushがGTMスニペットより前にあることを確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>/* SourcesタブでHTMLを確認。または */
-[...document.querySelectorAll('head script')].map(s =&gt; s.textContent.slice(0,80))</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>（コマンド不要）</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>head内で「window.dataLayer = window.dataLayer || []」およびuser_idのpushが、GTMスニペット（googletagmanager.com/gtm.js）より前に記述されていること。</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-004</t>
@@ -2826,32 +3837,85 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>【高】dataLayer初期化処理</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>任意ページを初回読み込み</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. ページ読み込み直後にConsoleを開く</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>window.dataLayer</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>配列が存在する（undefinedでない）。
 例: [{gtm.start: ..., event: 'gtm.js'}, ...]</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>【高】GTMスニペットが1回のみ設置されている</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>任意ページ</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. ページソースで gtm.js を検索
+2. Console で gtm.start の件数を確認</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'gtm.js').length</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1（GTMスニペットが重複していないこと）。2以上はNG。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2864,17 +3928,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2885,41 +3952,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-010</t>
@@ -2927,26 +4009,31 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】ログイン時：user_id/area_id/staff_id/member_r送信</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>取引先・担当者でログイン済み</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. 任意ページを読み込み
 2. ConsoleでdataLayerを確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>dataLayer.find(d =&gt; d.user_id)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>オブジェクトが返り、以下のキーが存在する:
   user_id: '取引先ID'（文字列）
@@ -2956,10 +4043,16 @@
 例: {user_id: 'C00001', area_id: 'A01', staff_id: 'S00001', member_r: 0}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-011</t>
@@ -2967,34 +4060,45 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】未ログイン時：user_idキーを出力しない</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>未ログイン（ゲスト）状態</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. ログアウトまたはシークレットウィンドウで任意ページを開く
 2. dataLayerを確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; 'user_id' in d)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>空配列 [] が返る（user_idキーを持つオブジェクトが存在しない）。</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-012</t>
@@ -3002,36 +4106,47 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【中】member_rの数値マッピング（0〜3）</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>会員ランクが異なる取引先のテストアカウントを用意</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>会員ランクが異なるテストアカウント</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. 標準(0)/シルバー(1)/ゴールド(2)/その他(3)の各アカウントでログイン
 2. それぞれdataLayerを確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>dataLayer.find(d =&gt; d.member_r !== undefined).member_r</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>ランクに応じた数値が返る:
   標準=0, シルバー=1, ゴールド=2, その他=3
 ※文字列ではなく数値型であること（typeof === 'number'）</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-013</t>
@@ -3039,33 +4154,86 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>【中】ページリロード時のdataLayer再出力</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>ログイン済み</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. ページ読み込み後にdataLayer件数を記録
 2. ページをリロード（F5）
 3. 再度件数を確認</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>dataLayer.length  // リロード前後で実行</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>リロード後はdataLayerがリセットされ、再度pushされる（リロードのたびに共通pushが出力される）。</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>【中】通常ページ表示時にloginイベントを送信しない</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ログイン済み。ログイン操作直後ではない通常ページ</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. ログイン済み状態でトップ等をフルリロード
+2. login イベントの有無を確認</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'login')</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>[]。通常ページ表示だけでは login は送信されない。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3078,17 +4246,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3099,41 +4270,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-020</t>
@@ -3141,36 +4327,47 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】ログイン成功時にloginイベント送信</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>未ログイン。有効なテストアカウントあり</t>
-        </is>
-      </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>未ログイン。有効なテストアカウント</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. ログイン画面で正しいID/PWを入力してログイン
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'login')</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1件以上の配列が返る。
 例: [{event: 'login'}]
 ※eventキーのみ。他の余計なキーがないこと。</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-021</t>
@@ -3178,34 +4375,45 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】ログイン失敗時はloginイベントを送信しない</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>未ログイン</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. 意図的に誤ったID/PWでログイン試行
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'login')</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>[] （空配列）。loginイベントはpushされない。</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-022</t>
@@ -3213,32 +4421,249 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【高】会員登録成功時にsign_upイベント送信</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>会員登録フォームにアクセス可能</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. 会員登録フォームに必要事項を入力して送信
 2. サーバー側で登録成功後、Consoleで確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'sign_up')</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>例: [{event: 'sign_up'}]</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>【高】会員登録失敗時はsign_upイベントを送信しない</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>会員登録フォームにアクセス可能</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1. 会員登録フォームに必要事項を入力して送信
+2. サーバー側で登録失敗後、Consoleで確認</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'sign_up')</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>[] （空配列）。sign_upイベントはpushされない。</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>【高】会員登録成功時：mailmagazine_signup（subscription_status=all）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>会員登録フォーム。メルマガ「全て受け取る」を選択可能</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. メルマガ受信設定を「全て受け取る」にして登録成功
+2. sign_up と mailmagazine_signup を確認</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; ['sign_up','mailmagazine_signup'].includes(d.event)).map(d =&gt; ({ event: d.event, subscription_status: d.subscription_status }))</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>sign_up と mailmagazine_signup の両方が存在。mailmagazine_signup は subscription_status: 'all'。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>【中】会員登録成功時：mailmagazine_signup（subscription_status=text_only）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>会員登録フォーム。メルマガ「テキストのみ」を選択可能</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1. メルマガ受信設定を「テキストのみ」にして登録成功
+2. Consoleで確認</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'mailmagazine_signup').pop()?.subscription_status</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>'text_only'</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="130" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>【中】会員登録成功時：mailmagazine_signup（subscription_status=none）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>会員登録フォーム。メルマガ「受け取らない」を選択可能</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1. メルマガ受信設定を「受け取らない」にして登録成功
+2. Consoleで確認</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'mailmagazine_signup').pop()?.subscription_status</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>'none'</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>【高】会員登録失敗時はmailmagazine_signupを送信しない</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>会員登録フォーム</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1. 登録失敗（バリデーションエラー等）を発生させる
+2. sign_up / mailmagazine_signup を確認</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; ['sign_up','mailmagazine_signup'].includes(d.event))</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>[]。登録失敗時は sign_up も mailmagazine_signup も送信しない。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3251,17 +4676,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3272,41 +4700,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-030</t>
@@ -3314,34 +4757,41 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】見積書DL時にquote_downloadイベント送信</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>見積書がDL可能な状態（見積依頼済み）</t>
-        </is>
-      </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>見積書DL可能な状態</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. 見積書DLリンクをクリック
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'quote_download')</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>例: [{event: 'quote_download'}]</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-031</t>
@@ -3349,35 +4799,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】見積依頼成功時：generate_lead（lead_source=quote）+items</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>ログイン済み。見積依頼フォームにアクセス可能</t>
-        </is>
-      </c>
       <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ログイン済み。新規見積依頼可能</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. 商品を選択して見積依頼フォームを送信（新規見積。再見積ではない）
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'generate_lead').map(d =&gt; ({event:d.event, lead_source:d.lead_source, items:d.ecommerce?.items}))</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>例: [{event: 'generate_lead', lead_source: 'quote', items: [{item_id:'...', item_name:'...', item_brand:'...', item_category1:'...', ..., price:9000, quantity:1}]}]
 ※lead_source='quote'、ecommerce.currency='JPY'、items配列あり</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-032</t>
@@ -3385,35 +4842,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【高】問い合わせ成功時：generate_lead（lead_source=inquiry）</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>問い合わせフォームにアクセス可能</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. 問い合わせフォームを送信して成功
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'generate_lead')</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>例: [{event: 'generate_lead', lead_source: 'inquiry'}]
 ※lead_source='inquiry'。itemsは含まれない（またはecommerceなし）。</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-033</t>
@@ -3421,32 +4885,123 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>【高】再見積（re_quote）時はgenerate_leadを送信しない</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>再見積が可能な既存見積あり</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>再見積可能な既存見積あり</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. 既存見積に対して再見積を依頼
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'generate_lead')</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>再見積操作後もgenerate_leadイベントは追加されない（件数が増えない）。</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>【高】見積依頼バリデーションエラー時はgenerate_leadを送信しない</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>見積依頼フォームにアクセス可能</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. 必須項目未入力等で送信しバリデーションエラーを発生
+2. Consoleで確認</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'generate_lead')</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>[]。バリデーションエラー時は generate_lead を送信しない。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="130" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>【高】問い合わせ送信失敗時はgenerate_leadを送信しない</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>問い合わせフォームにアクセス可能</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1. 必須項目未入力等で送信しエラーを発生
+2. Consoleで確認</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'generate_lead')</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>[]。送信失敗時は generate_lead を送信しない。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3459,17 +5014,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3480,41 +5038,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-040</t>
@@ -3522,36 +5095,43 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】商品詳細表示時：view_item + stock</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>商品詳細ページにアクセス可能</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. 商品詳細ページを表示
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'view_item').map(d =&gt; d.ecommerce.items[0])</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>items[0]に以下が含まれる:
   item_id, item_name, item_brand, item_category1〜5, price(数値), quantity(数値), stock(数値)
 例: {item_id:'hinban00002', ..., stock: 216, price: 9000, quantity: 1}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-041</t>
@@ -3559,35 +5139,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】カート追加成功時：add_to_cart（add_method=normal）</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>ログイン済み。商品詳細からカート追加可能</t>
-        </is>
-      </c>
       <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ログイン済み。カート追加可能</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. 商品詳細から通常操作でカートに追加
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_to_cart')</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>例: [{event:'add_to_cart', add_method:'normal', ecommerce:{value:9000, currency:'JPY', items:[...]}}]
 ※直前に{ecommerce:null}がpushされていること</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-042</t>
@@ -3595,34 +5182,41 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【中】add_to_cart：add_method=quick_order</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>クイックオーダー機能にアクセス可能</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>クイックオーダー利用可能</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. クイックオーダー経由でカートに追加
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_to_cart').pop().add_method</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>'quick_order'</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-043</t>
@@ -3630,34 +5224,41 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>【中】add_to_cart：add_method=order_history</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>購入履歴からの再注文が可能</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. 購入履歴から商品をカートに追加
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_to_cart').pop().add_method</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>'order_history'</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="120" customHeight="1">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-044</t>
@@ -3665,34 +5266,41 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>【中】add_to_cart：add_method=quote_history</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>見積履歴からのカート追加が可能</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. 見積履歴から商品をカートに追加
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_to_cart').pop().add_method</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>'quote_history'</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="120" customHeight="1">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TC-045</t>
@@ -3700,34 +5308,41 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>【高】カート削除時：remove_from_cart</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>カートに商品が入っている</t>
-        </is>
-      </c>
       <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>カートに商品あり</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. カート画面で商品を削除
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'remove_from_cart')</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>例: [{event:'remove_from_cart', ecommerce:{value:9000, currency:'JPY', items:[...]}}]</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8" ht="120" customHeight="1">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="130" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-046</t>
@@ -3735,34 +5350,41 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>【高】お気に入り追加時：add_to_wishlist</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>商品詳細ページにアクセス可能</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. お気に入りボタンをクリック
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_to_wishlist')</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>例: [{event:'add_to_wishlist', ecommerce:{currency:'JPY', items:[...]}}]</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="120" customHeight="1">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="130" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TC-047</t>
@@ -3770,32 +5392,82 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>【高】ecommerceイベント前にecommerce:nullをpush</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ecommerce系イベント（view_item等）を発火させる操作</t>
-        </is>
-      </c>
       <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce系イベントを発火させる操作</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. 商品詳細表示やカート追加を実行
 2. dataLayer全体を確認</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>(() =&gt; { const i = dataLayer.findIndex(d =&gt; d.event === 'view_item'); return i &gt;= 1 ? dataLayer[i-1] : null; })()</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>ecommerceイベントの直前の要素が {ecommerce: null} であること。</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="130" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>【高】カート追加失敗時はadd_to_cartを送信しない</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>カート追加失敗を再現できる（在庫切れ・数量エラー等）</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1. 操作前の add_to_cart 件数を記録
+2. カート追加失敗を発生
+3. 件数を比較</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'add_to_cart').length</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>失敗操作後も件数が増えない。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3808,17 +5480,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3829,41 +5504,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-050</t>
@@ -3871,34 +5561,41 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】注文プロセス開始：begin_checkout（cart_type=normal）</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>通常カートに商品あり</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. カートから注文プロセスへ進む（決済・配送指定画面表示）
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'begin_checkout')</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>例: [{event:'begin_checkout', cart_type:'normal', request_item_count:0, ecommerce:{value:..., currency:'JPY', items:[...]}}]</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-051</t>
@@ -3906,34 +5603,41 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】begin_checkout（cart_type=quote）</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>見積カートに商品あり</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. 見積カートから注文プロセスへ進む
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'begin_checkout').pop().cart_type</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>'quote'</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-052</t>
@@ -3941,36 +5645,43 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【中】request_item_countの値（あり/なし=0）</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>リクエスト注文を含む/含まないケース両方</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>リクエスト注文あり/なしの両ケース</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1-A. 通常商品のみで注文プロセス開始
 1-B. リクエスト注文商品を含めて開始
 2. それぞれ確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'begin_checkout').pop().request_item_count</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>通常のみ: 0（数値）
 リクエスト注文含む: 3等の正の整数</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-060</t>
@@ -3978,36 +5689,43 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>【高】add_shipping_infoとadd_payment_infoの同時送信</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>注文プロセス中。配送・決済情報を入力可能</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>注文プロセス中</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. 配送先・決済方法を入力して送信（サーバー受理成功）
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; ['add_shipping_info','add_payment_info'].includes(d.event)).map(d =&gt; d.event)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>['add_shipping_info', 'add_payment_info'] の両方が含まれる（同時送信）。
 ※add_shipping_infoにshipping_tierは仕様に無いがcouponあり
 ※add_payment_infoにpayment_typeあり</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="120" customHeight="1">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-061</t>
@@ -4015,34 +5733,41 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>【中】payment_typeの値（4種）</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>各決済方法で注文可能なテスト環境</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>各決済方法で注文可能</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. 自社掛け/代引き/銀行振込/全額ポイントの各決済で送信
 2. それぞれpayment_typeを確認</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_payment_info').pop().payment_type</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>on_credit / cash_on_delivery / bank_transfer / full_point のいずれか</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="120" customHeight="1">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TC-062</t>
@@ -4050,32 +5775,124 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>【中】クーポンコード（ecommerce.coupon）の送信</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>【中】クーポン適用時：ecommerce.couponの送信</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>クーポン適用可能な注文</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. クーポンコードを適用して配送・決済情報を送信
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'add_shipping_info').pop().ecommerce.coupon</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>クーポンコード文字列が返る（例: 'COUPON001'）。未適用時はキーごと省略（推奨仕様①）。</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="130" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-063</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>【中】クーポン未適用時：couponキーを出力しない</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>クーポン未適用の注文</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1. クーポンなしで配送・決済情報を送信
+2. coupon キーの有無を確認</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>'coupon' in (dataLayer.filter(d =&gt; d.event === 'add_shipping_info').pop()?.ecommerce || {})</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>false（coupon キーごと省略）。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-064</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>【高】配送・決済情報のサーバー受理失敗時はadd_shipping_info/add_payment_infoを送信しない</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>配送・決済情報の送信失敗を再現できる</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1. 操作前の件数を記録
+2. サーバー受理失敗を発生
+3. 件数を比較</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; ['add_shipping_info','add_payment_info'].includes(d.event)).length</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>失敗操作後も件数が増えない。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4088,17 +5905,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4109,41 +5929,56 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>前提条件</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>確認コマンド（Console）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期待結果（コマンド出力）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>実際の出力結果</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>エビデンス（スクショ/ファイル名）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="130" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-070</t>
@@ -4151,34 +5986,41 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>【高】承認申請時：approval_request（order_id）</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>承認フロー対象の注文が可能</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. 注文確認画面で承認申請ボタンを押下
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'approval_request')</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>例: [{event:'approval_request', order_id:'T_00012345'}]</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="130" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-071</t>
@@ -4186,34 +6028,41 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>【高】注文確定時：purchase（承認なし）</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>承認不要の注文が可能</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. 注文確定ボタンを押下して注文完了
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'purchase')</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>例: [{event:'purchase', order_id:'T_00012345', customer_type:'new', point_amount:500, cart_type:'normal', request_item_count:3, ecommerce:{transaction_id:'T_00012345', value:9000, tax:900, shipping:500, currency:'JPY', coupon:'...', items:[...]}}]</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-072</t>
@@ -4221,34 +6070,41 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>【高】承認あり：承認完了時にpurchase送信</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>承認フロー対象の注文。承認者アカウントあり</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>承認フロー対象。承認者アカウントあり</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. 承認申請 → 承認者が承認ボタン押下・処理完了
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'purchase')</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>承認完了時にpurchaseが送信される（申請時ではない）。</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-073</t>
@@ -4256,34 +6112,41 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>【高】決済エラー時はpurchaseを送信しない</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>決済エラーを意図的に発生させられる環境</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>決済エラーを再現できる</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. 決済エラーになる条件で注文確定を試行
 2. Consoleで確認</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'purchase')</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>purchaseイベントは追加されない（件数が増えない）。</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="120" customHeight="1">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="130" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-074</t>
@@ -4291,15 +6154,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>【高】customer_type（new/returning/guest）</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>初回購入/リピート/ゲストの各ケース</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>初回/リピート/ゲストの各ケース</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1-A. 初回購入の取引先で注文
 1-B. 2回目以降の取引先で注文
@@ -4307,20 +6175,22 @@
 2. customer_typeを確認</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>dataLayer.filter(d =&gt; d.event === 'purchase').pop().customer_type</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>new / returning / guest のいずれか</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="120" customHeight="1">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="130" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TC-075</t>
@@ -4328,32 +6198,123 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>【高】order_id = transaction_id = approval_request.order_id</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>承認フローありの注文完了</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. 承認申請→承認→購入完了
 2. 各イベントのIDを比較</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>(() =&gt; { const ar = dataLayer.find(d=&gt;d.event==='approval_request'); const pu = dataLayer.find(d=&gt;d.event==='purchase'); return {approval: ar?.order_id, transaction: pu?.ecommerce?.transaction_id, order: pu?.order_id}; })()</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3つの値がすべて同一（例: 'T_00012345'）。</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="130" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>【高】承認不要の注文でapproval_requestを送信しない</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>承認不要の注文が可能</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1. 承認不要で注文確定
+2. approval_request の有無を確認</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'approval_request')</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>[]。承認不要注文では approval_request を送信しない。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>【高】承認申請のみではpurchaseを送信しない</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>承認フロー対象の注文</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1. 承認申請のみ実行（承認完了前）
+2. purchase の有無を確認</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>dataLayer.filter(d =&gt; d.event === 'purchase')</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>[]。承認申請時点では purchase を送信しない。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
